--- a/data/trans_dic/P15D$nada-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P15D$nada-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no tuvo consecuencias el último accidente</t>
+          <t>Población que no tuvo consecuencias el último accidente (tasa de respuesta: 89,03%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,29; 69,98</t>
+          <t>10,26; 77,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,54; 30,78</t>
+          <t>5,4; 30,08</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,94</t>
+          <t>0,0; 27,49</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9,04; 41,44</t>
+          <t>9,39; 41,34</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,56; 42,98</t>
+          <t>7,88; 42,45</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,98</t>
+          <t>0,0; 23,79</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,53; 30,9</t>
+          <t>10,34; 31,52</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,81; 47,73</t>
+          <t>5,17; 44,33</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10,2; 28,35</t>
+          <t>10,07; 28,91</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,05; 16,97</t>
+          <t>2,07; 17,0</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>12,46; 30,25</t>
+          <t>12,24; 31,15</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 57,91</t>
+          <t>0,0; 57,75</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,99; 24,69</t>
+          <t>3,13; 26,28</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,95; 38,45</t>
+          <t>5,18; 38,64</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,91; 55,45</t>
+          <t>8,96; 58,92</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,39</t>
+          <t>0,0; 45,31</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,85; 37,17</t>
+          <t>6,08; 40,69</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,83; 58,34</t>
+          <t>8,29; 59,34</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,63; 33,07</t>
+          <t>9,33; 32,82</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,23</t>
+          <t>0,0; 37,29</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5,17; 25,29</t>
+          <t>6,42; 26,53</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9,59; 41,15</t>
+          <t>9,3; 38,83</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>12,31; 38,43</t>
+          <t>12,35; 39,04</t>
         </is>
       </c>
     </row>
@@ -997,22 +997,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,84; 44,69</t>
+          <t>4,89; 47,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>31,11; 57,43</t>
+          <t>33,03; 57,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,21; 38,16</t>
+          <t>4,22; 40,19</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,73; 34,78</t>
+          <t>7,38; 39,13</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1022,37 +1022,37 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>38,99; 72,65</t>
+          <t>40,39; 71,6</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,15</t>
+          <t>0,0; 34,89</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>15,13; 42,09</t>
+          <t>14,85; 41,86</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8,27; 47,76</t>
+          <t>8,23; 46,93</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>38,55; 59,0</t>
+          <t>38,78; 59,68</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,36; 27,48</t>
+          <t>4,23; 26,55</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>14,16; 33,21</t>
+          <t>13,62; 32,86</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,28; 52,69</t>
+          <t>10,06; 50,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,88; 24,25</t>
+          <t>2,87; 24,5</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,45; 30,49</t>
+          <t>3,58; 29,63</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,69</t>
+          <t>0,0; 35,14</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>18,89; 80,61</t>
+          <t>18,54; 82,91</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,52</t>
+          <t>0,0; 35,62</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,64; 22,86</t>
+          <t>2,63; 23,61</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,26; 27,05</t>
+          <t>2,27; 27,32</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>19,67; 54,57</t>
+          <t>19,73; 54,58</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,93; 21,9</t>
+          <t>3,69; 21,86</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,21; 21,05</t>
+          <t>4,59; 20,09</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,83; 23,3</t>
+          <t>2,94; 23,26</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 67,81</t>
+          <t>0,0; 67,9</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,31</t>
+          <t>0,0; 37,61</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 54,42</t>
+          <t>0,0; 55,68</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,73; 37,36</t>
+          <t>4,84; 37,74</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,58</t>
+          <t>0,0; 37,28</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,97; 23,04</t>
+          <t>2,95; 23,22</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,81</t>
+          <t>0,0; 29,61</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,23</t>
+          <t>0,0; 54,87</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10,19; 74,61</t>
+          <t>9,95; 75,6</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>27,33; 64,5</t>
+          <t>27,63; 64,01</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15,76; 47,41</t>
+          <t>15,4; 47,65</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>23,14; 55,86</t>
+          <t>21,74; 55,34</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>8,15; 67,31</t>
+          <t>7,94; 57,93</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>16,96; 49,2</t>
+          <t>16,77; 47,32</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,48; 27,14</t>
+          <t>3,51; 30,08</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>21,38; 47,09</t>
+          <t>20,86; 47,84</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>10,57; 53,19</t>
+          <t>10,37; 53,86</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>26,81; 51,55</t>
+          <t>26,12; 50,44</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>10,71; 30,72</t>
+          <t>11,75; 30,87</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>24,55; 46,25</t>
+          <t>24,82; 45,63</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>16,99; 52,79</t>
+          <t>16,94; 54,65</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>19,57; 42,06</t>
+          <t>20,47; 43,11</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7,63; 38,85</t>
+          <t>8,0; 41,93</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,27</t>
+          <t>0,0; 18,37</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,41; 44,62</t>
+          <t>5,22; 44,47</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,52; 40,08</t>
+          <t>16,35; 40,97</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,87; 48,29</t>
+          <t>10,44; 45,95</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>8,37; 30,81</t>
+          <t>8,05; 31,14</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>16,66; 44,51</t>
+          <t>16,94; 44,99</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>21,87; 38,17</t>
+          <t>21,32; 37,66</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12,29; 36,06</t>
+          <t>12,43; 34,96</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5,05; 20,34</t>
+          <t>5,55; 20,17</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>9,14; 40,6</t>
+          <t>7,93; 43,19</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,74; 32,2</t>
+          <t>3,76; 31,07</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,95; 29,39</t>
+          <t>4,75; 33,94</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,64; 31,02</t>
+          <t>0,61; 26,86</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,43</t>
+          <t>0,0; 18,92</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,3; 42,79</t>
+          <t>8,32; 42,29</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,11; 36,42</t>
+          <t>7,08; 38,43</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>5,9; 26,57</t>
+          <t>5,61; 25,49</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>5,3; 24,2</t>
+          <t>5,49; 24,23</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8,28; 30,72</t>
+          <t>8,42; 29,86</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7,71; 26,53</t>
+          <t>7,21; 26,44</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>5,37; 20,61</t>
+          <t>5,01; 20,77</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>19,7; 36,19</t>
+          <t>18,6; 34,57</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>20,5; 30,95</t>
+          <t>19,99; 30,72</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>11,06; 22,02</t>
+          <t>11,44; 22,29</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>11,56; 23,56</t>
+          <t>11,69; 23,0</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>10,23; 24,85</t>
+          <t>9,93; 25,17</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>22,3; 34,01</t>
+          <t>22,37; 34,44</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,28; 20,55</t>
+          <t>9,48; 20,02</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>15,21; 24,68</t>
+          <t>15,48; 24,77</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>17,24; 28,3</t>
+          <t>16,9; 28,12</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>23,1; 30,95</t>
+          <t>22,83; 30,25</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>11,93; 19,28</t>
+          <t>11,93; 19,08</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>14,66; 22,03</t>
+          <t>14,81; 22,01</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no tuvo consecuencias el último accidente</t>
+          <t>Población que no tuvo consecuencias el último accidente (tasa de respuesta: 89,03%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>957; 6504</t>
+          <t>953; 7221</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2052; 11402</t>
+          <t>2000; 11139</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 5366</t>
+          <t>0; 5280</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2540; 11642</t>
+          <t>2639; 11612</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 1872</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2366; 11872</t>
+          <t>2176; 11726</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 7842</t>
+          <t>0; 7183</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3051; 8954</t>
+          <t>2995; 9135</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>951; 7818</t>
+          <t>847; 7261</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6598; 18332</t>
+          <t>6512; 18691</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1011; 8381</t>
+          <t>1023; 8397</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>7112; 17265</t>
+          <t>6983; 17777</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 4547</t>
+          <t>0; 4535</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>930; 7674</t>
+          <t>972; 8169</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>961; 7465</t>
+          <t>1005; 7502</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1682; 13499</t>
+          <t>2181; 14343</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 4069</t>
+          <t>0; 4061</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1166; 11246</t>
+          <t>1841; 12312</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1085; 9263</t>
+          <t>1316; 9422</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3213; 11034</t>
+          <t>3113; 10948</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 6091</t>
+          <t>0; 6270</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3169; 15512</t>
+          <t>3937; 16276</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3384; 14522</t>
+          <t>3282; 13705</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7101; 22176</t>
+          <t>7129; 22526</t>
         </is>
       </c>
     </row>
@@ -2625,22 +2625,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>883; 8147</t>
+          <t>892; 8640</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>16444; 30354</t>
+          <t>17457; 30157</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>978; 8865</t>
+          <t>981; 9336</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1650; 7418</t>
+          <t>1574; 8347</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -2650,37 +2650,37 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15535; 28942</t>
+          <t>16092; 28526</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 5018</t>
+          <t>0; 4843</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4053; 11279</t>
+          <t>3980; 11216</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1855; 10714</t>
+          <t>1847; 10528</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>35736; 54685</t>
+          <t>35944; 55319</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1619; 10198</t>
+          <t>1569; 9853</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6816; 15984</t>
+          <t>6554; 15813</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1832; 9389</t>
+          <t>1793; 8959</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>877; 7396</t>
+          <t>876; 7472</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1324; 11705</t>
+          <t>1375; 11377</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 9901</t>
+          <t>0; 8345</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1849; 7895</t>
+          <t>1815; 8120</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 5997</t>
+          <t>0; 5849</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>960; 8316</t>
+          <t>955; 8586</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>412; 4926</t>
+          <t>414; 4976</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5432; 15068</t>
+          <t>5448; 15070</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1844; 10277</t>
+          <t>1732; 10257</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3149; 15735</t>
+          <t>3431; 15022</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1188; 9779</t>
+          <t>1233; 9763</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 4963</t>
+          <t>0; 4969</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 1777</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 4284</t>
+          <t>0; 3808</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 3871</t>
+          <t>0; 3960</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 1815</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>936; 7396</t>
+          <t>958; 7472</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 1486</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 417</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 5987</t>
+          <t>0; 5639</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>981; 7598</t>
+          <t>974; 7655</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0; 4824</t>
+          <t>0; 3988</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0; 3461</t>
+          <t>0; 4199</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>906; 6635</t>
+          <t>885; 6723</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>8294; 19578</t>
+          <t>8385; 19427</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4449; 13382</t>
+          <t>4347; 13450</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6025; 14542</t>
+          <t>5659; 14406</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>864; 7136</t>
+          <t>841; 6141</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6008; 17423</t>
+          <t>5938; 16757</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1268; 9894</t>
+          <t>1279; 10968</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>5773; 12714</t>
+          <t>5630; 12914</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2061; 10370</t>
+          <t>2022; 10500</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>17634; 33905</t>
+          <t>17176; 33173</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>6927; 19869</t>
+          <t>7603; 19969</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>13019; 24525</t>
+          <t>13164; 24195</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>4635; 14402</t>
+          <t>4622; 14911</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>12675; 27238</t>
+          <t>13257; 27919</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2016; 10269</t>
+          <t>2115; 11085</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 7503</t>
+          <t>0; 7981</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>996; 8216</t>
+          <t>961; 8188</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10452; 23920</t>
+          <t>9754; 24447</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2978; 13235</t>
+          <t>2861; 12593</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>4194; 15438</t>
+          <t>4033; 15602</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>7615; 20340</t>
+          <t>7742; 20560</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>27218; 47499</t>
+          <t>26534; 46866</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6616; 19414</t>
+          <t>6695; 18823</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>4725; 19031</t>
+          <t>5195; 18869</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2413; 10715</t>
+          <t>2093; 11398</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>899; 7731</t>
+          <t>904; 7462</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1021; 10171</t>
+          <t>1644; 11746</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>167; 8051</t>
+          <t>158; 6971</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0; 5232</t>
+          <t>0; 5096</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2100; 10832</t>
+          <t>2106; 10706</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1901; 9736</t>
+          <t>1893; 10274</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>1688; 7602</t>
+          <t>1606; 7292</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>2828; 12905</t>
+          <t>2926; 12918</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>4086; 15151</t>
+          <t>4154; 14730</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>4729; 16276</t>
+          <t>4421; 16217</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>2929; 11247</t>
+          <t>2735; 11332</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>24250; 44542</t>
+          <t>22894; 42545</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>58173; 87817</t>
+          <t>56722; 87176</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>22072; 43968</t>
+          <t>22845; 44501</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>23136; 47135</t>
+          <t>23395; 46013</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>9594; 23310</t>
+          <t>9318; 23607</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>56707; 86513</t>
+          <t>56893; 87597</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>17651; 39101</t>
+          <t>18046; 38099</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>32488; 52725</t>
+          <t>33063; 52911</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>37386; 61372</t>
+          <t>36652; 60982</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>124316; 166554</t>
+          <t>122858; 162758</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>46506; 75176</t>
+          <t>46519; 74381</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>60643; 91146</t>
+          <t>61252; 91050</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P15D$nada-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P15D$nada-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>20,22%</t>
         </is>
       </c>
     </row>
@@ -717,22 +717,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,26; 77,69</t>
+          <t>10,3; 76,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,4; 30,08</t>
+          <t>5,25; 29,44</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,49</t>
+          <t>0,0; 22,89</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9,39; 41,34</t>
+          <t>8,66; 36,22</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -742,37 +742,37 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,88; 42,45</t>
+          <t>7,73; 42,86</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,79</t>
+          <t>0,0; 23,23</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,34; 31,52</t>
+          <t>11,47; 31,8</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,17; 44,33</t>
+          <t>5,81; 45,14</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10,07; 28,91</t>
+          <t>10,44; 29,3</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,07; 17,0</t>
+          <t>2,03; 15,9</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>12,24; 31,15</t>
+          <t>12,66; 29,87</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>21,42%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 57,75</t>
+          <t>0,0; 44,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,13; 26,28</t>
+          <t>3,02; 26,32</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,18; 38,64</t>
+          <t>5,18; 38,82</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,96; 58,92</t>
+          <t>6,03; 54,12</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,31</t>
+          <t>0,0; 53,3</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,08; 40,69</t>
+          <t>3,8; 38,42</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,29; 59,34</t>
+          <t>7,09; 58,17</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,33; 32,82</t>
+          <t>8,59; 33,38</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,29</t>
+          <t>0,0; 32,39</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6,42; 26,53</t>
+          <t>5,27; 23,77</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9,3; 38,83</t>
+          <t>10,44; 40,22</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>12,35; 39,04</t>
+          <t>11,88; 35,44</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>21,85%</t>
         </is>
       </c>
     </row>
@@ -997,22 +997,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,89; 47,4</t>
+          <t>5,28; 46,41</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>33,03; 57,06</t>
+          <t>33,03; 57,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,22; 40,19</t>
+          <t>4,14; 40,13</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,38; 39,13</t>
+          <t>6,92; 33,64</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1022,37 +1022,37 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>40,39; 71,6</t>
+          <t>39,6; 71,75</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,89</t>
+          <t>0,0; 30,86</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>14,85; 41,86</t>
+          <t>15,42; 41,48</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8,23; 46,93</t>
+          <t>8,72; 48,77</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>38,78; 59,68</t>
+          <t>39,2; 59,19</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,23; 26,55</t>
+          <t>4,8; 27,69</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>13,62; 32,86</t>
+          <t>13,58; 31,25</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,39%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,06; 50,28</t>
+          <t>10,55; 52,51</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,87; 24,5</t>
+          <t>2,87; 24,26</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,58; 29,63</t>
+          <t>2,9; 28,84</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,14</t>
+          <t>0,0; 30,8</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>18,54; 82,91</t>
+          <t>18,1; 80,91</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,62</t>
+          <t>0,0; 36,88</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,63; 23,61</t>
+          <t>2,56; 21,72</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,27; 27,32</t>
+          <t>2,58; 26,25</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>19,73; 54,58</t>
+          <t>19,89; 53,81</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,69; 21,86</t>
+          <t>3,84; 20,87</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,59; 20,09</t>
+          <t>4,48; 20,79</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,94; 23,26</t>
+          <t>3,03; 23,36</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>18,51%</t>
         </is>
       </c>
     </row>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 67,9</t>
+          <t>0,0; 68,16</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1287,12 +1287,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,61</t>
+          <t>0,0; 37,67</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 55,68</t>
+          <t>0,0; 56,96</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,84; 37,74</t>
+          <t>4,86; 37,77</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1317,22 +1317,22 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,28</t>
+          <t>0,0; 44,35</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,95; 23,22</t>
+          <t>3,01; 25,58</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,61</t>
+          <t>0,0; 32,86</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 54,87</t>
+          <t>0,0; 55,65</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>36,99%</t>
+          <t>35,96%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>31,01%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>33,39%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9,95; 75,6</t>
+          <t>10,17; 72,39</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>27,63; 64,01</t>
+          <t>27,32; 65,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15,4; 47,65</t>
+          <t>14,97; 47,47</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>21,74; 55,34</t>
+          <t>23,59; 54,67</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7,94; 57,93</t>
+          <t>8,19; 61,17</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>16,77; 47,32</t>
+          <t>16,71; 48,62</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,51; 30,08</t>
+          <t>3,01; 29,1</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>20,86; 47,84</t>
+          <t>20,63; 44,89</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>10,37; 53,86</t>
+          <t>10,3; 54,14</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>26,12; 50,44</t>
+          <t>25,84; 50,0</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>11,75; 30,87</t>
+          <t>10,24; 30,7</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>24,82; 45,63</t>
+          <t>24,32; 43,72</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>9,6%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>16,94; 54,65</t>
+          <t>17,08; 53,49</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>20,47; 43,11</t>
+          <t>20,67; 43,38</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8,0; 41,93</t>
+          <t>8,0; 39,25</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,37</t>
+          <t>0,0; 15,41</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,22; 44,47</t>
+          <t>5,39; 45,67</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,35; 40,97</t>
+          <t>16,49; 41,12</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,44; 45,95</t>
+          <t>11,12; 45,6</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>8,05; 31,14</t>
+          <t>7,23; 26,57</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>16,94; 44,99</t>
+          <t>16,58; 44,22</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>21,32; 37,66</t>
+          <t>21,5; 37,82</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12,43; 34,96</t>
+          <t>12,26; 36,98</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5,55; 20,17</t>
+          <t>5,31; 18,26</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,34%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>7,93; 43,19</t>
+          <t>8,94; 40,85</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,76; 31,07</t>
+          <t>3,68; 30,98</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4,75; 33,94</t>
+          <t>2,98; 29,27</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,61; 26,86</t>
+          <t>2,26; 30,8</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,92</t>
+          <t>0,0; 18,72</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,32; 42,29</t>
+          <t>8,49; 40,6</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,08; 38,43</t>
+          <t>6,84; 36,17</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>5,61; 25,49</t>
+          <t>4,45; 23,81</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>5,49; 24,23</t>
+          <t>5,22; 24,33</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8,42; 29,86</t>
+          <t>8,41; 30,89</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7,21; 26,44</t>
+          <t>8,25; 27,14</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>5,01; 20,77</t>
+          <t>5,46; 20,5</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>16,94%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>18,6; 34,57</t>
+          <t>18,72; 34,58</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>19,99; 30,72</t>
+          <t>19,97; 30,39</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>11,44; 22,29</t>
+          <t>11,67; 22,43</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>11,69; 23,0</t>
+          <t>11,09; 21,2</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>9,93; 25,17</t>
+          <t>10,6; 25,71</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>22,37; 34,44</t>
+          <t>22,94; 34,6</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,48; 20,02</t>
+          <t>9,54; 19,95</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>15,48; 24,77</t>
+          <t>14,46; 22,74</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>16,9; 28,12</t>
+          <t>16,71; 28,17</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>22,83; 30,25</t>
+          <t>22,87; 30,76</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>11,93; 19,08</t>
+          <t>11,7; 19,02</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>14,81; 22,01</t>
+          <t>14,12; 20,41</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6038</t>
+          <t>5538</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5599</t>
+          <t>6083</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11637</t>
+          <t>11621</t>
         </is>
       </c>
     </row>
@@ -2209,22 +2209,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>953; 7221</t>
+          <t>957; 7127</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2000; 11139</t>
+          <t>1946; 10902</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 5280</t>
+          <t>0; 4396</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2639; 11612</t>
+          <t>2342; 9794</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2234,37 +2234,37 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2176; 11726</t>
+          <t>2136; 11838</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 7183</t>
+          <t>0; 7012</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2995; 9135</t>
+          <t>3492; 9678</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>847; 7261</t>
+          <t>953; 7394</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6512; 18691</t>
+          <t>6752; 18943</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1023; 8397</t>
+          <t>1005; 7855</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6983; 17777</t>
+          <t>7278; 17168</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6501</t>
+          <t>6297</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>6384</t>
+          <t>6433</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>12885</t>
+          <t>12731</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 4535</t>
+          <t>0; 3514</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>972; 8169</t>
+          <t>938; 8180</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1005; 7502</t>
+          <t>1006; 7538</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2181; 14343</t>
+          <t>1489; 13368</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 4061</t>
+          <t>0; 4778</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1841; 12312</t>
+          <t>1151; 11624</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1316; 9422</t>
+          <t>1126; 9235</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3113; 10948</t>
+          <t>2985; 11593</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 6270</t>
+          <t>0; 5446</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3937; 16276</t>
+          <t>3234; 14579</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3282; 13705</t>
+          <t>3683; 14194</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7129; 22526</t>
+          <t>7058; 21061</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3746</t>
+          <t>3674</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7093</t>
+          <t>7034</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10838</t>
+          <t>10708</t>
         </is>
       </c>
     </row>
@@ -2625,22 +2625,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>892; 8640</t>
+          <t>962; 8460</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>17457; 30157</t>
+          <t>17459; 30310</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>981; 9336</t>
+          <t>962; 9323</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1574; 8347</t>
+          <t>1545; 7505</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -2650,37 +2650,37 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16092; 28526</t>
+          <t>15778; 28586</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 4843</t>
+          <t>0; 4284</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3980; 11216</t>
+          <t>4117; 11077</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1847; 10528</t>
+          <t>1956; 10941</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>35944; 55319</t>
+          <t>36335; 54869</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1569; 9853</t>
+          <t>1783; 10276</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6554; 15813</t>
+          <t>6656; 15316</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1753</t>
+          <t>1971</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>1918</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>3671</t>
+          <t>3985</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1793; 8959</t>
+          <t>1881; 9355</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>876; 7472</t>
+          <t>876; 7398</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1375; 11377</t>
+          <t>1114; 11074</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 8345</t>
+          <t>0; 8654</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1815; 8120</t>
+          <t>1773; 7923</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 5849</t>
+          <t>0; 6057</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>955; 8586</t>
+          <t>931; 7899</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>414; 4976</t>
+          <t>501; 5093</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5448; 15070</t>
+          <t>5493; 14859</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1732; 10257</t>
+          <t>1801; 9794</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3431; 15022</t>
+          <t>3347; 15545</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1233; 9763</t>
+          <t>1438; 11096</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1364</t>
+          <t>1484</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1364</t>
+          <t>1484</t>
         </is>
       </c>
     </row>
@@ -3041,7 +3041,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 4969</t>
+          <t>0; 4989</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -3051,12 +3051,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 3808</t>
+          <t>0; 3814</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 3960</t>
+          <t>0; 4267</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -3066,7 +3066,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>958; 7472</t>
+          <t>962; 7477</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -3081,22 +3081,22 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 5639</t>
+          <t>0; 6708</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>974; 7655</t>
+          <t>991; 8433</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0; 3988</t>
+          <t>0; 4426</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0; 4199</t>
+          <t>0; 4461</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9630</t>
+          <t>9357</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>8710</t>
+          <t>8724</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>18340</t>
+          <t>18081</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>885; 6723</t>
+          <t>905; 6438</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>8385; 19427</t>
+          <t>8291; 19728</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4347; 13450</t>
+          <t>4225; 13399</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5659; 14406</t>
+          <t>6138; 14225</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>841; 6141</t>
+          <t>869; 6485</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5938; 16757</t>
+          <t>5919; 17219</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1279; 10968</t>
+          <t>1098; 10609</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>5630; 12914</t>
+          <t>5804; 12628</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2022; 10500</t>
+          <t>2008; 10555</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>17176; 33173</t>
+          <t>16993; 32885</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7603; 19969</t>
+          <t>6622; 19856</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>13164; 24195</t>
+          <t>13167; 23675</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1690</t>
+          <t>2467</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>8156</t>
+          <t>8495</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>9846</t>
+          <t>10962</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>4622; 14911</t>
+          <t>4661; 14595</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>13257; 27919</t>
+          <t>13385; 28094</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2115; 11085</t>
+          <t>2114; 10377</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 7981</t>
+          <t>0; 8598</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>961; 8188</t>
+          <t>993; 8410</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9754; 24447</t>
+          <t>9842; 24540</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2861; 12593</t>
+          <t>3047; 12498</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>4033; 15602</t>
+          <t>4224; 15526</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>7742; 20560</t>
+          <t>7576; 20208</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>26534; 46866</t>
+          <t>26749; 47061</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6695; 18823</t>
+          <t>6604; 19912</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>5195; 18869</t>
+          <t>6071; 20864</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2348</t>
+          <t>3074</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>3728</t>
+          <t>4117</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>6075</t>
+          <t>7191</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2093; 11398</t>
+          <t>2359; 10779</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>904; 7462</t>
+          <t>883; 7439</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1644; 11746</t>
+          <t>1031; 10130</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>158; 6971</t>
+          <t>667; 9106</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0; 5096</t>
+          <t>0; 5042</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2106; 10706</t>
+          <t>2149; 10277</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1893; 10274</t>
+          <t>1828; 9671</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>1606; 7292</t>
+          <t>1507; 8052</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>2926; 12918</t>
+          <t>2781; 12975</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>4154; 14730</t>
+          <t>4148; 15238</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>4421; 16217</t>
+          <t>5062; 16648</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>2735; 11332</t>
+          <t>3458; 12991</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>33070</t>
+          <t>33861</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>41588</t>
+          <t>42901</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>74658</t>
+          <t>76762</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>22894; 42545</t>
+          <t>23046; 42555</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>56722; 87176</t>
+          <t>56671; 86248</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>22845; 44501</t>
+          <t>23303; 44783</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>23395; 46013</t>
+          <t>24518; 46864</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>9318; 23607</t>
+          <t>9943; 24120</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>56893; 87597</t>
+          <t>58345; 87992</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>18046; 38099</t>
+          <t>18150; 37960</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>33063; 52911</t>
+          <t>33584; 52788</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>36652; 60982</t>
+          <t>36241; 61094</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>122858; 162758</t>
+          <t>123051; 165548</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>46519; 74381</t>
+          <t>45605; 74175</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>61252; 91050</t>
+          <t>63985; 92485</t>
         </is>
       </c>
     </row>
